--- a/BROMappings/Mapping en definitie BRO GMN.xlsx
+++ b/BROMappings/Mapping en definitie BRO GMN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/MATLAB/Menyanthes/Meny_OS/trunk/BronDatamodel/BROMappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{DFE48FA1-484F-4F3E-BCD5-80D38728AFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4355BCD3-93C1-46EC-8C91-07F46339AE07}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{DFE48FA1-484F-4F3E-BCD5-80D38728AFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C517A82D-89BF-4116-8668-7EE9D744F91F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,30 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$25</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="142">
   <si>
     <t>Registratieobject</t>
   </si>
@@ -421,6 +432,39 @@
   </si>
   <si>
     <t>[DateTime]</t>
+  </si>
+  <si>
+    <t>ProviderID</t>
+  </si>
+  <si>
+    <t>ID van het meetpunt bij de dataleverancier (bijv in de portal bij telemetrische data)</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>naam</t>
+  </si>
+  <si>
+    <t>De naam waaronder het monitoringnet bekend is</t>
+  </si>
+  <si>
+    <t>Afgeleid</t>
+  </si>
+  <si>
+    <t>Ja</t>
+  </si>
+  <si>
+    <t>meetpuntcode</t>
+  </si>
+  <si>
+    <t>GMW-BRO-ID</t>
+  </si>
+  <si>
+    <t>Dit moet op of na de inrichtingsdatum van de laatste put liggen. Afgeleid als waarde bij de QC-Wizard, elders niet.</t>
+  </si>
+  <si>
+    <t>Afgeleid als [Putcode_buisnr ] bij de QC-Wizard, elders niet</t>
   </si>
 </sst>
 </file>
@@ -831,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T228"/>
+  <dimension ref="A1:T230"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -847,7 +891,7 @@
     <col min="11" max="11" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="37.28515625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="161" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="17" width="25.28515625" customWidth="1"/>
     <col min="18" max="18" width="26.28515625" customWidth="1"/>
     <col min="19" max="19" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -1095,7 +1139,7 @@
         <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G5" t="s">
         <v>102</v>
@@ -1304,20 +1348,20 @@
       <c r="N9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>77</v>
+      <c r="O9" t="s">
+        <v>136</v>
+      </c>
+      <c r="P9" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>136</v>
       </c>
       <c r="R9" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="1" t="s">
-        <v>121</v>
+      <c r="S9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1379,16 +1423,16 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1397,19 +1441,19 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="O11" t="s">
         <v>59</v>
       </c>
       <c r="P11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S11" t="s">
         <v>121</v>
@@ -1427,10 +1471,10 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
         <v>76</v>
@@ -1445,16 +1489,16 @@
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O12" t="s">
         <v>59</v>
       </c>
       <c r="P12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R12" t="s">
         <v>76</v>
@@ -1463,562 +1507,660 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13"/>
+      <c r="C13" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="N13" t="s">
+        <v>70</v>
+      </c>
+      <c r="O13" t="s">
+        <v>59</v>
+      </c>
+      <c r="P13" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>80</v>
+      </c>
+      <c r="R13" t="s">
+        <v>76</v>
+      </c>
+      <c r="S13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1" t="s">
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="P14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="15" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="8">
-        <v>1</v>
-      </c>
-      <c r="K14" s="8">
-        <v>1</v>
-      </c>
-      <c r="O14" s="8" t="s">
+      <c r="J15" s="8">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1</v>
+      </c>
+      <c r="O15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="P14" s="8" t="s">
+      <c r="P15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="Q14" s="8" t="s">
+      <c r="Q15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="R14" s="8" t="s">
+      <c r="R15" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="S14" s="8" t="s">
+      <c r="S15" s="8" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="T15" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>48</v>
       </c>
-      <c r="B15"/>
-      <c r="C15" t="s">
+      <c r="B16"/>
+      <c r="C16" t="s">
         <v>58</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>46</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>92</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>93</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G16" t="s">
         <v>130</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H16" t="s">
         <v>52</v>
       </c>
-      <c r="J15">
+      <c r="J16">
         <v>0</v>
       </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="N15"/>
-      <c r="O15" t="s">
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="N16"/>
+      <c r="O16" t="s">
         <v>59</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P16" t="s">
         <v>95</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="Q16" t="s">
         <v>94</v>
       </c>
-      <c r="R15" t="s">
+      <c r="R16" t="s">
         <v>83</v>
       </c>
-      <c r="S15" t="s">
+      <c r="S16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="F17" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="T17" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>48</v>
       </c>
-      <c r="B17"/>
-      <c r="C17" t="s">
+      <c r="B18"/>
+      <c r="C18" t="s">
         <v>57</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>47</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>36</v>
       </c>
-      <c r="F17" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F18" t="s">
+        <v>139</v>
+      </c>
+      <c r="G18" t="s">
         <v>102</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H18" t="s">
         <v>53</v>
       </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
         <v>7</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N18" t="s">
         <v>63</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O18" t="s">
         <v>61</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P18" t="s">
         <v>122</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q18" t="s">
         <v>122</v>
       </c>
-      <c r="R17" t="s">
+      <c r="R18" t="s">
         <v>102</v>
       </c>
-      <c r="S17" t="s">
+      <c r="S18" t="s">
         <v>121</v>
       </c>
-      <c r="T17" t="s">
+      <c r="T18" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O18" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="S18" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>48</v>
       </c>
-      <c r="B19"/>
-      <c r="C19" t="s">
+      <c r="B20"/>
+      <c r="C20" t="s">
         <v>91</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>45</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E20" t="s">
         <v>5</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F20" t="s">
         <v>42</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G20" t="s">
         <v>76</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H20" t="s">
         <v>51</v>
       </c>
-      <c r="J19">
+      <c r="J20">
         <v>0</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K20" t="s">
         <v>7</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N20" t="s">
         <v>66</v>
       </c>
-      <c r="O19" t="s">
+      <c r="O20" t="s">
         <v>60</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P20" t="s">
         <v>82</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="Q20" t="s">
         <v>82</v>
       </c>
-      <c r="R19" t="s">
+      <c r="R20" t="s">
         <v>76</v>
       </c>
-      <c r="S19" t="s">
+      <c r="S20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J21" s="1">
         <v>0</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O20" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="Q21" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="R21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21"/>
-      <c r="C21" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L21" t="s">
-        <v>111</v>
-      </c>
-      <c r="M21" t="s">
-        <v>111</v>
-      </c>
-      <c r="O21" t="s">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22"/>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M22" t="s">
+        <v>111</v>
+      </c>
+      <c r="O22" t="s">
         <v>60</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P22" t="s">
         <v>115</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q22" t="s">
         <v>115</v>
       </c>
-      <c r="R21" t="s">
+      <c r="R22" t="s">
         <v>113</v>
       </c>
-      <c r="S21" t="s">
+      <c r="S22" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="O22" s="1" t="s">
+    <row r="23" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:20" s="11" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="O23" s="11" t="s">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P24" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>131</v>
+      </c>
+      <c r="R24" t="s">
+        <v>126</v>
+      </c>
+      <c r="S24" t="s">
+        <v>121</v>
+      </c>
+      <c r="T24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" s="11" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="O25" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="P23" s="11" t="s">
+      <c r="P25" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="Q23" s="11" t="s">
+      <c r="Q25" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="R23" s="11" t="s">
+      <c r="R25" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="S23" s="11" t="s">
+      <c r="S25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="T23" s="11" t="s">
+      <c r="T25" s="11" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24"/>
-      <c r="B24"/>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="N24"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="N25"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26"/>
@@ -2265,8 +2407,10 @@
     <row r="226" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="227" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="228" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="229" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="230" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:T23" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T25" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
